--- a/data/raw/Taxonomias_MatrizBD.xlsx
+++ b/data/raw/Taxonomias_MatrizBD.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f15395a9ed9a48f/Proyectos_DS/Analisis_Curricular/Analisis_Curriculo/proyecto_analisis_microcurricular/data/raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_949D9DBC2E50F17918366A1687F0E3155C7FC255" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4D13822D-2EE5-4F99-9775-9FA6DF4606BC}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="11_949D9DBC2E50F17918366A1687F0E3155C7FC255" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{295A7C14-E46D-4F99-9B47-5C3AF5008A68}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,6 +18,9 @@
     <sheet name="Subcategorias" sheetId="2" r:id="rId3"/>
     <sheet name="Matriz_BD" sheetId="4" r:id="rId4"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Verbos!$A$1:$F$647</definedName>
+  </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
@@ -1604,6 +1607,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:F647"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -7175,7 +7179,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="279" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A279" s="3">
         <v>278</v>
       </c>
@@ -7195,7 +7199,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="280" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A280" s="3">
         <v>279</v>
       </c>
@@ -7215,7 +7219,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="281" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A281" s="3">
         <v>280</v>
       </c>
@@ -7235,7 +7239,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="282" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A282" s="3">
         <v>281</v>
       </c>
@@ -7255,7 +7259,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="283" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A283" s="3">
         <v>282</v>
       </c>
@@ -7275,7 +7279,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="284" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A284" s="3">
         <v>283</v>
       </c>
@@ -7295,7 +7299,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="285" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A285" s="3">
         <v>284</v>
       </c>
@@ -7315,7 +7319,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="286" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A286" s="3">
         <v>285</v>
       </c>
@@ -7335,7 +7339,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="287" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A287" s="3">
         <v>286</v>
       </c>
@@ -7355,7 +7359,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="288" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A288" s="3">
         <v>287</v>
       </c>
@@ -7375,7 +7379,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="289" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A289" s="3">
         <v>288</v>
       </c>
@@ -7395,7 +7399,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="290" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A290" s="3">
         <v>289</v>
       </c>
@@ -7415,7 +7419,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="291" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A291" s="3">
         <v>290</v>
       </c>
@@ -7435,7 +7439,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="292" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A292" s="3">
         <v>291</v>
       </c>
@@ -7455,7 +7459,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="293" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A293" s="3">
         <v>292</v>
       </c>
@@ -7475,7 +7479,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="294" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A294" s="3">
         <v>293</v>
       </c>
@@ -7495,7 +7499,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="295" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A295" s="3">
         <v>294</v>
       </c>
@@ -7515,7 +7519,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="296" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A296" s="3">
         <v>295</v>
       </c>
@@ -7535,7 +7539,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="297" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A297" s="3">
         <v>296</v>
       </c>
@@ -7555,7 +7559,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="298" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A298" s="3">
         <v>297</v>
       </c>
@@ -7575,7 +7579,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="299" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A299" s="3">
         <v>298</v>
       </c>
@@ -7595,7 +7599,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="300" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A300" s="3">
         <v>299</v>
       </c>
@@ -7615,7 +7619,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="301" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A301" s="3">
         <v>300</v>
       </c>
@@ -7635,7 +7639,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="302" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A302" s="3">
         <v>301</v>
       </c>
@@ -7655,7 +7659,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="303" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A303" s="3">
         <v>302</v>
       </c>
@@ -7675,7 +7679,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="304" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A304" s="3">
         <v>303</v>
       </c>
@@ -7695,7 +7699,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="305" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A305" s="3">
         <v>304</v>
       </c>
@@ -7715,7 +7719,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="306" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A306" s="3">
         <v>305</v>
       </c>
@@ -7735,7 +7739,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="307" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A307" s="3">
         <v>306</v>
       </c>
@@ -7755,7 +7759,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="308" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A308" s="3">
         <v>307</v>
       </c>
@@ -7775,7 +7779,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="309" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A309" s="3">
         <v>308</v>
       </c>
@@ -7795,7 +7799,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="310" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A310" s="3">
         <v>309</v>
       </c>
@@ -7815,7 +7819,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="311" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A311" s="3">
         <v>310</v>
       </c>
@@ -7835,7 +7839,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="312" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A312" s="3">
         <v>311</v>
       </c>
@@ -7855,7 +7859,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="313" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A313" s="3">
         <v>312</v>
       </c>
@@ -7875,7 +7879,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="314" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A314" s="3">
         <v>313</v>
       </c>
@@ -7895,7 +7899,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="315" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A315" s="3">
         <v>314</v>
       </c>
@@ -7915,7 +7919,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="316" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A316" s="3">
         <v>315</v>
       </c>
@@ -7935,7 +7939,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="317" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A317" s="3">
         <v>316</v>
       </c>
@@ -7955,7 +7959,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="318" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A318" s="3">
         <v>317</v>
       </c>
@@ -7975,7 +7979,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="319" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A319" s="3">
         <v>318</v>
       </c>
@@ -7995,7 +7999,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="320" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A320" s="3">
         <v>319</v>
       </c>
@@ -8015,7 +8019,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="321" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A321" s="3">
         <v>320</v>
       </c>
@@ -8035,7 +8039,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="322" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A322" s="3">
         <v>321</v>
       </c>
@@ -8055,7 +8059,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="323" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A323" s="3">
         <v>322</v>
       </c>
@@ -8075,7 +8079,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="324" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A324" s="3">
         <v>323</v>
       </c>
@@ -8095,7 +8099,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="325" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A325" s="3">
         <v>324</v>
       </c>
@@ -8115,7 +8119,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="326" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A326" s="3">
         <v>325</v>
       </c>
@@ -8135,7 +8139,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="327" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A327" s="3">
         <v>326</v>
       </c>
@@ -8155,7 +8159,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="328" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A328" s="3">
         <v>327</v>
       </c>
@@ -8175,7 +8179,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="329" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A329" s="3">
         <v>328</v>
       </c>
@@ -8195,7 +8199,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="330" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A330" s="3">
         <v>329</v>
       </c>
@@ -8215,7 +8219,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="331" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A331" s="3">
         <v>330</v>
       </c>
@@ -8235,7 +8239,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="332" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A332" s="3">
         <v>331</v>
       </c>
@@ -8255,7 +8259,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="333" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A333" s="3">
         <v>332</v>
       </c>
@@ -8275,7 +8279,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="334" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A334" s="3">
         <v>333</v>
       </c>
@@ -8295,7 +8299,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="335" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A335" s="3">
         <v>334</v>
       </c>
@@ -8315,7 +8319,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="336" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A336" s="3">
         <v>335</v>
       </c>
@@ -8335,7 +8339,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="337" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A337" s="3">
         <v>336</v>
       </c>
@@ -8355,7 +8359,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="338" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A338" s="3">
         <v>337</v>
       </c>
@@ -8375,7 +8379,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="339" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A339" s="3">
         <v>338</v>
       </c>
@@ -8395,7 +8399,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="340" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A340" s="3">
         <v>339</v>
       </c>
@@ -8415,7 +8419,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="341" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A341" s="3">
         <v>340</v>
       </c>
@@ -8435,7 +8439,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="342" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A342" s="3">
         <v>341</v>
       </c>
@@ -8455,7 +8459,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="343" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A343" s="3">
         <v>342</v>
       </c>
@@ -8475,7 +8479,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="344" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A344" s="3">
         <v>343</v>
       </c>
@@ -8495,7 +8499,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="345" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A345" s="3">
         <v>344</v>
       </c>
@@ -8515,7 +8519,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="346" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A346" s="3">
         <v>345</v>
       </c>
@@ -8535,7 +8539,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="347" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A347" s="3">
         <v>346</v>
       </c>
@@ -8555,7 +8559,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="348" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A348" s="3">
         <v>347</v>
       </c>
@@ -8575,7 +8579,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="349" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A349" s="3">
         <v>348</v>
       </c>
@@ -8595,7 +8599,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="350" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A350" s="3">
         <v>349</v>
       </c>
@@ -8615,7 +8619,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="351" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A351" s="3">
         <v>350</v>
       </c>
@@ -8635,7 +8639,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="352" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A352" s="3">
         <v>351</v>
       </c>
@@ -8655,7 +8659,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="353" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A353" s="3">
         <v>352</v>
       </c>
@@ -8675,7 +8679,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="354" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A354" s="3">
         <v>353</v>
       </c>
@@ -8695,7 +8699,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="355" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A355" s="3">
         <v>354</v>
       </c>
@@ -8715,7 +8719,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="356" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A356" s="3">
         <v>355</v>
       </c>
@@ -8735,7 +8739,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="357" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A357" s="3">
         <v>356</v>
       </c>
@@ -8755,7 +8759,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="358" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A358" s="3">
         <v>357</v>
       </c>
@@ -8775,7 +8779,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="359" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A359" s="3">
         <v>358</v>
       </c>
@@ -8795,7 +8799,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="360" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A360" s="3">
         <v>359</v>
       </c>
@@ -8815,7 +8819,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="361" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A361" s="3">
         <v>360</v>
       </c>
@@ -8835,7 +8839,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="362" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A362" s="3">
         <v>361</v>
       </c>
@@ -8855,7 +8859,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="363" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A363" s="3">
         <v>362</v>
       </c>
@@ -8875,7 +8879,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="364" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A364" s="3">
         <v>363</v>
       </c>
@@ -8895,7 +8899,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="365" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A365" s="3">
         <v>364</v>
       </c>
@@ -8915,7 +8919,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="366" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A366" s="3">
         <v>365</v>
       </c>
@@ -8935,7 +8939,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="367" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A367" s="3">
         <v>366</v>
       </c>
@@ -8955,7 +8959,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="368" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A368" s="3">
         <v>367</v>
       </c>
@@ -8975,7 +8979,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="369" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A369" s="3">
         <v>368</v>
       </c>
@@ -8995,7 +8999,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="370" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A370" s="3">
         <v>369</v>
       </c>
@@ -9015,7 +9019,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="371" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A371" s="3">
         <v>370</v>
       </c>
@@ -9035,7 +9039,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="372" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A372" s="3">
         <v>371</v>
       </c>
@@ -9055,7 +9059,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="373" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A373" s="3">
         <v>372</v>
       </c>
@@ -9075,7 +9079,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="374" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A374" s="3">
         <v>373</v>
       </c>
@@ -9095,7 +9099,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="375" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A375" s="3">
         <v>374</v>
       </c>
@@ -9115,7 +9119,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="376" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A376" s="3">
         <v>375</v>
       </c>
@@ -9135,7 +9139,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="377" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A377" s="3">
         <v>376</v>
       </c>
@@ -9155,7 +9159,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="378" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A378" s="3">
         <v>377</v>
       </c>
@@ -9175,7 +9179,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="379" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A379" s="3">
         <v>378</v>
       </c>
@@ -9195,7 +9199,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="380" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A380" s="3">
         <v>379</v>
       </c>
@@ -9215,7 +9219,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="381" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A381" s="3">
         <v>380</v>
       </c>
@@ -9235,7 +9239,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="382" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A382" s="3">
         <v>381</v>
       </c>
@@ -9255,7 +9259,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="383" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A383" s="3">
         <v>382</v>
       </c>
@@ -9275,7 +9279,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="384" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A384" s="3">
         <v>383</v>
       </c>
@@ -9295,7 +9299,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="385" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A385" s="3">
         <v>384</v>
       </c>
@@ -9315,7 +9319,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="386" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A386" s="3">
         <v>385</v>
       </c>
@@ -9335,7 +9339,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="387" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="387" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A387" s="3">
         <v>386</v>
       </c>
@@ -9355,7 +9359,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="388" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="388" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A388" s="3">
         <v>387</v>
       </c>
@@ -9375,7 +9379,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="389" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="389" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A389" s="3">
         <v>388</v>
       </c>
@@ -9395,7 +9399,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="390" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="390" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A390" s="3">
         <v>389</v>
       </c>
@@ -9415,7 +9419,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="391" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="391" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A391" s="3">
         <v>390</v>
       </c>
@@ -9435,7 +9439,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="392" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="392" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A392" s="3">
         <v>391</v>
       </c>
@@ -9455,7 +9459,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="393" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="393" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A393" s="3">
         <v>392</v>
       </c>
@@ -9475,7 +9479,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="394" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="394" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A394" s="3">
         <v>393</v>
       </c>
@@ -9495,7 +9499,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="395" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="395" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A395" s="3">
         <v>394</v>
       </c>
@@ -9515,7 +9519,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="396" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="396" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A396" s="3">
         <v>395</v>
       </c>
@@ -9535,7 +9539,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="397" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="397" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A397" s="3">
         <v>396</v>
       </c>
@@ -9555,7 +9559,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="398" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="398" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A398" s="3">
         <v>397</v>
       </c>
@@ -9575,7 +9579,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="399" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="399" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A399" s="3">
         <v>398</v>
       </c>
@@ -9595,7 +9599,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="400" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="400" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A400" s="3">
         <v>399</v>
       </c>
@@ -9615,7 +9619,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="401" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="401" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A401" s="3">
         <v>400</v>
       </c>
@@ -9635,7 +9639,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="402" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="402" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A402" s="3">
         <v>401</v>
       </c>
@@ -9655,7 +9659,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="403" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="403" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A403" s="3">
         <v>402</v>
       </c>
@@ -9675,7 +9679,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="404" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="404" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A404" s="3">
         <v>403</v>
       </c>
@@ -9695,7 +9699,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="405" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="405" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A405" s="3">
         <v>404</v>
       </c>
@@ -9715,7 +9719,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="406" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="406" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A406" s="3">
         <v>405</v>
       </c>
@@ -9735,7 +9739,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="407" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="407" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A407" s="3">
         <v>406</v>
       </c>
@@ -9755,7 +9759,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="408" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="408" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A408" s="3">
         <v>407</v>
       </c>
@@ -9775,7 +9779,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="409" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="409" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A409" s="3">
         <v>408</v>
       </c>
@@ -9795,7 +9799,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="410" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="410" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A410" s="3">
         <v>409</v>
       </c>
@@ -9815,7 +9819,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="411" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="411" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A411" s="3">
         <v>410</v>
       </c>
@@ -9835,7 +9839,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="412" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="412" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A412" s="3">
         <v>411</v>
       </c>
@@ -9855,7 +9859,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="413" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="413" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A413" s="3">
         <v>412</v>
       </c>
@@ -9875,7 +9879,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="414" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="414" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A414" s="3">
         <v>413</v>
       </c>
@@ -9895,7 +9899,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="415" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="415" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A415" s="3">
         <v>414</v>
       </c>
@@ -9915,7 +9919,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="416" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="416" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A416" s="3">
         <v>415</v>
       </c>
@@ -9935,7 +9939,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="417" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="417" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A417" s="3">
         <v>416</v>
       </c>
@@ -9955,7 +9959,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="418" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="418" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A418" s="3">
         <v>417</v>
       </c>
@@ -9975,7 +9979,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="419" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="419" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A419" s="3">
         <v>418</v>
       </c>
@@ -9995,7 +9999,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="420" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="420" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A420" s="3">
         <v>419</v>
       </c>
@@ -10015,7 +10019,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="421" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="421" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A421" s="3">
         <v>420</v>
       </c>
@@ -10035,7 +10039,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="422" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="422" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A422" s="3">
         <v>421</v>
       </c>
@@ -10055,7 +10059,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="423" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="423" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A423" s="3">
         <v>422</v>
       </c>
@@ -10075,7 +10079,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="424" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="424" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A424" s="3">
         <v>423</v>
       </c>
@@ -10095,7 +10099,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="425" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="425" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A425" s="3">
         <v>424</v>
       </c>
@@ -10115,7 +10119,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="426" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="426" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A426" s="3">
         <v>425</v>
       </c>
@@ -10135,7 +10139,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="427" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="427" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A427" s="3">
         <v>426</v>
       </c>
@@ -10155,7 +10159,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="428" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="428" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A428" s="3">
         <v>427</v>
       </c>
@@ -10175,7 +10179,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="429" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="429" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A429" s="3">
         <v>428</v>
       </c>
@@ -10195,7 +10199,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="430" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="430" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A430" s="3">
         <v>429</v>
       </c>
@@ -10215,7 +10219,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="431" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="431" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A431" s="3">
         <v>430</v>
       </c>
@@ -10235,7 +10239,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="432" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="432" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A432" s="3">
         <v>431</v>
       </c>
@@ -10255,7 +10259,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="433" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="433" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A433" s="3">
         <v>432</v>
       </c>
@@ -10275,7 +10279,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="434" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="434" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A434" s="3">
         <v>433</v>
       </c>
@@ -10295,7 +10299,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="435" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="435" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A435" s="3">
         <v>434</v>
       </c>
@@ -10315,7 +10319,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="436" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="436" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A436" s="3">
         <v>435</v>
       </c>
@@ -10335,7 +10339,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="437" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="437" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A437" s="3">
         <v>436</v>
       </c>
@@ -10355,7 +10359,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="438" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="438" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A438" s="3">
         <v>437</v>
       </c>
@@ -10375,7 +10379,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="439" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="439" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A439" s="3">
         <v>438</v>
       </c>
@@ -10395,7 +10399,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="440" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="440" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A440" s="3">
         <v>439</v>
       </c>
@@ -10415,7 +10419,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="441" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="441" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A441" s="3">
         <v>440</v>
       </c>
@@ -10435,7 +10439,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="442" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="442" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A442" s="3">
         <v>441</v>
       </c>
@@ -10455,7 +10459,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="443" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="443" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A443" s="3">
         <v>442</v>
       </c>
@@ -10475,7 +10479,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="444" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="444" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A444" s="3">
         <v>443</v>
       </c>
@@ -10495,7 +10499,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="445" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="445" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A445" s="3">
         <v>444</v>
       </c>
@@ -10515,7 +10519,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="446" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="446" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A446" s="3">
         <v>445</v>
       </c>
@@ -10535,7 +10539,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="447" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="447" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A447" s="3">
         <v>446</v>
       </c>
@@ -10555,7 +10559,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="448" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="448" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A448" s="3">
         <v>447</v>
       </c>
@@ -10575,7 +10579,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="449" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="449" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A449" s="3">
         <v>448</v>
       </c>
@@ -10595,7 +10599,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="450" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="450" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A450" s="3">
         <v>449</v>
       </c>
@@ -10615,7 +10619,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="451" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="451" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A451" s="3">
         <v>450</v>
       </c>
@@ -10635,7 +10639,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="452" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="452" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A452" s="3">
         <v>451</v>
       </c>
@@ -10655,7 +10659,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="453" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="453" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A453" s="3">
         <v>452</v>
       </c>
@@ -10675,7 +10679,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="454" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="454" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A454" s="3">
         <v>453</v>
       </c>
@@ -10695,7 +10699,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="455" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="455" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A455" s="3">
         <v>454</v>
       </c>
@@ -10715,7 +10719,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="456" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="456" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A456" s="3">
         <v>455</v>
       </c>
@@ -10735,7 +10739,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="457" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="457" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A457" s="3">
         <v>456</v>
       </c>
@@ -10755,7 +10759,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="458" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="458" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A458" s="3">
         <v>457</v>
       </c>
@@ -10775,7 +10779,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="459" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="459" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A459" s="3">
         <v>458</v>
       </c>
@@ -10795,7 +10799,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="460" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="460" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A460" s="3">
         <v>459</v>
       </c>
@@ -10815,7 +10819,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="461" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="461" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A461" s="3">
         <v>460</v>
       </c>
@@ -10835,7 +10839,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="462" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="462" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A462" s="3">
         <v>461</v>
       </c>
@@ -10855,7 +10859,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="463" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="463" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A463" s="3">
         <v>462</v>
       </c>
@@ -10875,7 +10879,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="464" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="464" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A464" s="3">
         <v>463</v>
       </c>
@@ -10895,7 +10899,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="465" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="465" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A465" s="3">
         <v>464</v>
       </c>
@@ -10915,7 +10919,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="466" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="466" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A466" s="3">
         <v>465</v>
       </c>
@@ -10935,7 +10939,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="467" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="467" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A467" s="3">
         <v>466</v>
       </c>
@@ -10955,7 +10959,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="468" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="468" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A468" s="3">
         <v>467</v>
       </c>
@@ -10975,7 +10979,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="469" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="469" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A469" s="3">
         <v>468</v>
       </c>
@@ -10995,7 +10999,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="470" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="470" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A470" s="3">
         <v>469</v>
       </c>
@@ -11015,7 +11019,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="471" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="471" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A471" s="3">
         <v>470</v>
       </c>
@@ -11035,7 +11039,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="472" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="472" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A472" s="3">
         <v>471</v>
       </c>
@@ -11055,7 +11059,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="473" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="473" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A473" s="3">
         <v>472</v>
       </c>
@@ -11075,7 +11079,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="474" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="474" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A474" s="3">
         <v>473</v>
       </c>
@@ -11095,7 +11099,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="475" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="475" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A475" s="3">
         <v>474</v>
       </c>
@@ -11115,7 +11119,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="476" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="476" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A476" s="3">
         <v>475</v>
       </c>
@@ -11135,7 +11139,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="477" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="477" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A477" s="3">
         <v>476</v>
       </c>
@@ -11155,7 +11159,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="478" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="478" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A478" s="3">
         <v>477</v>
       </c>
@@ -11175,7 +11179,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="479" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="479" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A479" s="3">
         <v>478</v>
       </c>
@@ -11195,7 +11199,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="480" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="480" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A480" s="3">
         <v>479</v>
       </c>
@@ -11215,7 +11219,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="481" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="481" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A481" s="3">
         <v>480</v>
       </c>
@@ -11235,7 +11239,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="482" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="482" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A482" s="3">
         <v>481</v>
       </c>
@@ -11255,7 +11259,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="483" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="483" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A483" s="3">
         <v>482</v>
       </c>
@@ -11275,7 +11279,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="484" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="484" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A484" s="3">
         <v>483</v>
       </c>
@@ -11295,7 +11299,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="485" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="485" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A485" s="3">
         <v>484</v>
       </c>
@@ -11315,7 +11319,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="486" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="486" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A486" s="3">
         <v>485</v>
       </c>
@@ -11335,7 +11339,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="487" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="487" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A487" s="3">
         <v>486</v>
       </c>
@@ -11355,7 +11359,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="488" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="488" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A488" s="3">
         <v>487</v>
       </c>
@@ -11375,7 +11379,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="489" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="489" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A489" s="3">
         <v>488</v>
       </c>
@@ -11395,7 +11399,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="490" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="490" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A490" s="3">
         <v>489</v>
       </c>
@@ -11415,7 +11419,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="491" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="491" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A491" s="4">
         <v>490</v>
       </c>
@@ -11435,7 +11439,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="492" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="492" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A492" s="4">
         <v>491</v>
       </c>
@@ -11455,7 +11459,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="493" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="493" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A493" s="4">
         <v>492</v>
       </c>
@@ -11475,7 +11479,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="494" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="494" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A494" s="4">
         <v>493</v>
       </c>
@@ -11495,7 +11499,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="495" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="495" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A495" s="4">
         <v>494</v>
       </c>
@@ -11515,7 +11519,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="496" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="496" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A496" s="4">
         <v>495</v>
       </c>
@@ -11535,7 +11539,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="497" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="497" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A497" s="4">
         <v>496</v>
       </c>
@@ -11555,7 +11559,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="498" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="498" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A498" s="4">
         <v>497</v>
       </c>
@@ -11575,7 +11579,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="499" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="499" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A499" s="4">
         <v>498</v>
       </c>
@@ -11595,7 +11599,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="500" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="500" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A500" s="4">
         <v>499</v>
       </c>
@@ -11615,7 +11619,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="501" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="501" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A501" s="4">
         <v>500</v>
       </c>
@@ -11635,7 +11639,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="502" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="502" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A502" s="4">
         <v>501</v>
       </c>
@@ -11655,7 +11659,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="503" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="503" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A503" s="4">
         <v>502</v>
       </c>
@@ -11675,7 +11679,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="504" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="504" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A504" s="4">
         <v>503</v>
       </c>
@@ -11695,7 +11699,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="505" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="505" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A505" s="4">
         <v>504</v>
       </c>
@@ -11715,7 +11719,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="506" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="506" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A506" s="4">
         <v>505</v>
       </c>
@@ -11735,7 +11739,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="507" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="507" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A507" s="4">
         <v>506</v>
       </c>
@@ -11755,7 +11759,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="508" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="508" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A508" s="4">
         <v>507</v>
       </c>
@@ -11775,7 +11779,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="509" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="509" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A509" s="4">
         <v>508</v>
       </c>
@@ -11795,7 +11799,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="510" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="510" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A510" s="4">
         <v>509</v>
       </c>
@@ -11815,7 +11819,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="511" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="511" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A511" s="4">
         <v>510</v>
       </c>
@@ -11835,7 +11839,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="512" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="512" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A512" s="4">
         <v>511</v>
       </c>
@@ -11855,7 +11859,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="513" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="513" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A513" s="4">
         <v>512</v>
       </c>
@@ -11875,7 +11879,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="514" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="514" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A514" s="4">
         <v>513</v>
       </c>
@@ -11895,7 +11899,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="515" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="515" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A515" s="4">
         <v>514</v>
       </c>
@@ -11915,7 +11919,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="516" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="516" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A516" s="4">
         <v>515</v>
       </c>
@@ -11935,7 +11939,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="517" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="517" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A517" s="4">
         <v>516</v>
       </c>
@@ -11955,7 +11959,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="518" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="518" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A518" s="4">
         <v>517</v>
       </c>
@@ -11975,7 +11979,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="519" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="519" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A519" s="4">
         <v>518</v>
       </c>
@@ -11995,7 +11999,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="520" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="520" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A520" s="4">
         <v>519</v>
       </c>
@@ -12015,7 +12019,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="521" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="521" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A521" s="4">
         <v>520</v>
       </c>
@@ -12035,7 +12039,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="522" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="522" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A522" s="4">
         <v>521</v>
       </c>
@@ -12055,7 +12059,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="523" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="523" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A523" s="4">
         <v>522</v>
       </c>
@@ -12075,7 +12079,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="524" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="524" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A524" s="4">
         <v>523</v>
       </c>
@@ -12095,7 +12099,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="525" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="525" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A525" s="4">
         <v>524</v>
       </c>
@@ -12115,7 +12119,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="526" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="526" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A526" s="4">
         <v>525</v>
       </c>
@@ -12135,7 +12139,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="527" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="527" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A527" s="4">
         <v>526</v>
       </c>
@@ -12155,7 +12159,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="528" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="528" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A528" s="4">
         <v>527</v>
       </c>
@@ -12175,7 +12179,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="529" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="529" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A529" s="4">
         <v>528</v>
       </c>
@@ -12195,7 +12199,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="530" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="530" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A530" s="4">
         <v>529</v>
       </c>
@@ -12215,7 +12219,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="531" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="531" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A531" s="4">
         <v>530</v>
       </c>
@@ -12235,7 +12239,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="532" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="532" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A532" s="4">
         <v>531</v>
       </c>
@@ -12255,7 +12259,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="533" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="533" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A533" s="4">
         <v>532</v>
       </c>
@@ -12275,7 +12279,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="534" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="534" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A534" s="4">
         <v>533</v>
       </c>
@@ -12295,7 +12299,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="535" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="535" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A535" s="4">
         <v>534</v>
       </c>
@@ -12315,7 +12319,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="536" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="536" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A536" s="4">
         <v>535</v>
       </c>
@@ -12335,7 +12339,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="537" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="537" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A537" s="4">
         <v>536</v>
       </c>
@@ -12355,7 +12359,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="538" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="538" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A538" s="4">
         <v>537</v>
       </c>
@@ -12375,7 +12379,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="539" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="539" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A539" s="4">
         <v>538</v>
       </c>
@@ -12395,7 +12399,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="540" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="540" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A540" s="4">
         <v>539</v>
       </c>
@@ -12415,7 +12419,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="541" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="541" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A541" s="4">
         <v>540</v>
       </c>
@@ -12435,7 +12439,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="542" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="542" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A542" s="4">
         <v>541</v>
       </c>
@@ -12455,7 +12459,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="543" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="543" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A543" s="4">
         <v>542</v>
       </c>
@@ -12475,7 +12479,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="544" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="544" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A544" s="4">
         <v>543</v>
       </c>
@@ -12495,7 +12499,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="545" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="545" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A545" s="4">
         <v>544</v>
       </c>
@@ -12515,7 +12519,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="546" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="546" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A546" s="4">
         <v>545</v>
       </c>
@@ -12535,7 +12539,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="547" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="547" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A547" s="4">
         <v>546</v>
       </c>
@@ -12555,7 +12559,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="548" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="548" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A548" s="4">
         <v>547</v>
       </c>
@@ -12575,7 +12579,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="549" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="549" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A549" s="4">
         <v>548</v>
       </c>
@@ -12595,7 +12599,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="550" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="550" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A550" s="4">
         <v>549</v>
       </c>
@@ -12615,7 +12619,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="551" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="551" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A551" s="4">
         <v>550</v>
       </c>
@@ -12635,7 +12639,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="552" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="552" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A552" s="4">
         <v>551</v>
       </c>
@@ -12655,7 +12659,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="553" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="553" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A553" s="4">
         <v>552</v>
       </c>
@@ -12675,7 +12679,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="554" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="554" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A554" s="4">
         <v>553</v>
       </c>
@@ -12695,7 +12699,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="555" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="555" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A555" s="4">
         <v>554</v>
       </c>
@@ -12715,7 +12719,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="556" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="556" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A556" s="4">
         <v>555</v>
       </c>
@@ -12735,7 +12739,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="557" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="557" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A557" s="4">
         <v>556</v>
       </c>
@@ -12755,7 +12759,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="558" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="558" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A558" s="4">
         <v>557</v>
       </c>
@@ -12775,7 +12779,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="559" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="559" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A559" s="4">
         <v>558</v>
       </c>
@@ -12795,7 +12799,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="560" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="560" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A560" s="4">
         <v>559</v>
       </c>
@@ -12815,7 +12819,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="561" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="561" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A561" s="4">
         <v>560</v>
       </c>
@@ -12835,7 +12839,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="562" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="562" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A562" s="4">
         <v>561</v>
       </c>
@@ -12855,7 +12859,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="563" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="563" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A563" s="4">
         <v>562</v>
       </c>
@@ -12875,7 +12879,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="564" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="564" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A564" s="4">
         <v>563</v>
       </c>
@@ -12895,7 +12899,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="565" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="565" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A565" s="4">
         <v>564</v>
       </c>
@@ -12915,7 +12919,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="566" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="566" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A566" s="4">
         <v>565</v>
       </c>
@@ -12935,7 +12939,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="567" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="567" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A567" s="4">
         <v>566</v>
       </c>
@@ -12955,7 +12959,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="568" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="568" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A568" s="4">
         <v>567</v>
       </c>
@@ -12975,7 +12979,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="569" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="569" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A569" s="4">
         <v>568</v>
       </c>
@@ -12995,7 +12999,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="570" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="570" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A570" s="4">
         <v>569</v>
       </c>
@@ -13015,7 +13019,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="571" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="571" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A571" s="4">
         <v>570</v>
       </c>
@@ -13035,7 +13039,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="572" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="572" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A572" s="4">
         <v>571</v>
       </c>
@@ -13055,7 +13059,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="573" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="573" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A573" s="4">
         <v>572</v>
       </c>
@@ -13075,7 +13079,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="574" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="574" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A574" s="4">
         <v>573</v>
       </c>
@@ -13095,7 +13099,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="575" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="575" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A575" s="4">
         <v>574</v>
       </c>
@@ -13115,7 +13119,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="576" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="576" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A576" s="4">
         <v>575</v>
       </c>
@@ -13135,7 +13139,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="577" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="577" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A577" s="4">
         <v>576</v>
       </c>
@@ -13155,7 +13159,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="578" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="578" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A578" s="4">
         <v>577</v>
       </c>
@@ -13175,7 +13179,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="579" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="579" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A579" s="4">
         <v>578</v>
       </c>
@@ -13195,7 +13199,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="580" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="580" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A580" s="4">
         <v>579</v>
       </c>
@@ -13215,7 +13219,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="581" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="581" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A581" s="4">
         <v>580</v>
       </c>
@@ -13235,7 +13239,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="582" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="582" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A582" s="4">
         <v>581</v>
       </c>
@@ -13255,7 +13259,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="583" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="583" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A583" s="4">
         <v>582</v>
       </c>
@@ -13275,7 +13279,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="584" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="584" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A584" s="4">
         <v>583</v>
       </c>
@@ -13295,7 +13299,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="585" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="585" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A585" s="4">
         <v>584</v>
       </c>
@@ -13315,7 +13319,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="586" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="586" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A586" s="4">
         <v>585</v>
       </c>
@@ -13335,7 +13339,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="587" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="587" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A587" s="4">
         <v>586</v>
       </c>
@@ -13355,7 +13359,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="588" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="588" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A588" s="4">
         <v>587</v>
       </c>
@@ -13375,7 +13379,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="589" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="589" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A589" s="4">
         <v>588</v>
       </c>
@@ -13395,7 +13399,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="590" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="590" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A590" s="4">
         <v>589</v>
       </c>
@@ -13415,7 +13419,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="591" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="591" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A591" s="4">
         <v>590</v>
       </c>
@@ -13435,7 +13439,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="592" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="592" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A592" s="4">
         <v>591</v>
       </c>
@@ -13455,7 +13459,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="593" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="593" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A593" s="4">
         <v>592</v>
       </c>
@@ -13475,7 +13479,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="594" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="594" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A594" s="4">
         <v>593</v>
       </c>
@@ -13495,7 +13499,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="595" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="595" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A595" s="4">
         <v>594</v>
       </c>
@@ -13515,7 +13519,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="596" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="596" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A596" s="4">
         <v>595</v>
       </c>
@@ -13535,7 +13539,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="597" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="597" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A597" s="4">
         <v>596</v>
       </c>
@@ -13555,7 +13559,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="598" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="598" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A598" s="4">
         <v>597</v>
       </c>
@@ -13575,7 +13579,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="599" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="599" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A599" s="4">
         <v>598</v>
       </c>
@@ -13595,7 +13599,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="600" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="600" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A600" s="4">
         <v>599</v>
       </c>
@@ -13615,7 +13619,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="601" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="601" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A601" s="4">
         <v>600</v>
       </c>
@@ -13635,7 +13639,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="602" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="602" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A602" s="4">
         <v>601</v>
       </c>
@@ -13655,7 +13659,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="603" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="603" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A603" s="4">
         <v>602</v>
       </c>
@@ -13675,7 +13679,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="604" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="604" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A604" s="4">
         <v>603</v>
       </c>
@@ -13695,7 +13699,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="605" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="605" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A605" s="4">
         <v>604</v>
       </c>
@@ -13715,7 +13719,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="606" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="606" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A606" s="4">
         <v>605</v>
       </c>
@@ -13735,7 +13739,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="607" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="607" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A607" s="4">
         <v>606</v>
       </c>
@@ -13755,7 +13759,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="608" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="608" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A608" s="4">
         <v>607</v>
       </c>
@@ -13775,7 +13779,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="609" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="609" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A609" s="4">
         <v>608</v>
       </c>
@@ -13795,7 +13799,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="610" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="610" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A610" s="4">
         <v>609</v>
       </c>
@@ -13815,7 +13819,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="611" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="611" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A611" s="4">
         <v>610</v>
       </c>
@@ -13835,7 +13839,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="612" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="612" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A612" s="4">
         <v>611</v>
       </c>
@@ -13855,7 +13859,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="613" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="613" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A613" s="4">
         <v>612</v>
       </c>
@@ -13875,7 +13879,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="614" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="614" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A614" s="4">
         <v>613</v>
       </c>
@@ -13895,7 +13899,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="615" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="615" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A615" s="4">
         <v>614</v>
       </c>
@@ -13915,7 +13919,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="616" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="616" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A616" s="4">
         <v>615</v>
       </c>
@@ -13935,7 +13939,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="617" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="617" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A617" s="4">
         <v>616</v>
       </c>
@@ -13955,7 +13959,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="618" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="618" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A618" s="4">
         <v>617</v>
       </c>
@@ -13975,7 +13979,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="619" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="619" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A619" s="4">
         <v>618</v>
       </c>
@@ -13995,7 +13999,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="620" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="620" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A620" s="4">
         <v>619</v>
       </c>
@@ -14015,7 +14019,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="621" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="621" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A621" s="4">
         <v>620</v>
       </c>
@@ -14035,7 +14039,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="622" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="622" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A622" s="4">
         <v>621</v>
       </c>
@@ -14055,7 +14059,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="623" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="623" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A623" s="4">
         <v>622</v>
       </c>
@@ -14075,7 +14079,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="624" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="624" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A624" s="4">
         <v>623</v>
       </c>
@@ -14095,7 +14099,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="625" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="625" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A625" s="4">
         <v>624</v>
       </c>
@@ -14115,7 +14119,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="626" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="626" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A626" s="4">
         <v>625</v>
       </c>
@@ -14135,7 +14139,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="627" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="627" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A627" s="4">
         <v>626</v>
       </c>
@@ -14155,7 +14159,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="628" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="628" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A628" s="4">
         <v>627</v>
       </c>
@@ -14175,7 +14179,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="629" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="629" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A629" s="4">
         <v>628</v>
       </c>
@@ -14195,7 +14199,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="630" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="630" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A630" s="4">
         <v>629</v>
       </c>
@@ -14215,7 +14219,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="631" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="631" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A631" s="4">
         <v>630</v>
       </c>
@@ -14235,7 +14239,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="632" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="632" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A632" s="4">
         <v>631</v>
       </c>
@@ -14255,7 +14259,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="633" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="633" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A633" s="4">
         <v>632</v>
       </c>
@@ -14275,7 +14279,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="634" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="634" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A634" s="4">
         <v>633</v>
       </c>
@@ -14295,7 +14299,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="635" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="635" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A635" s="4">
         <v>634</v>
       </c>
@@ -14315,7 +14319,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="636" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="636" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A636" s="4">
         <v>635</v>
       </c>
@@ -14335,7 +14339,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="637" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="637" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A637" s="4">
         <v>636</v>
       </c>
@@ -14355,7 +14359,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="638" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="638" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A638" s="4">
         <v>637</v>
       </c>
@@ -14375,7 +14379,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="639" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="639" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A639" s="4">
         <v>638</v>
       </c>
@@ -14395,7 +14399,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="640" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="640" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A640" s="4">
         <v>639</v>
       </c>
@@ -14415,7 +14419,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="641" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="641" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A641" s="4">
         <v>640</v>
       </c>
@@ -14435,7 +14439,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="642" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="642" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A642" s="4">
         <v>641</v>
       </c>
@@ -14455,7 +14459,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="643" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="643" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A643" s="4">
         <v>642</v>
       </c>
@@ -14475,7 +14479,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="644" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="644" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A644" s="4">
         <v>643</v>
       </c>
@@ -14495,7 +14499,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="645" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="645" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A645" s="4">
         <v>644</v>
       </c>
@@ -14515,7 +14519,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="646" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="646" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A646" s="4">
         <v>645</v>
       </c>
@@ -14535,7 +14539,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="647" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="647" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A647" s="4">
         <v>646</v>
       </c>
@@ -14556,6 +14560,13 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:F647" xr:uid="{00000000-0001-0000-0200-000000000000}">
+    <filterColumn colId="5">
+      <filters>
+        <filter val="Cognitivo()"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
